--- a/Process_Docs/SIQ.xlsx
+++ b/Process_Docs/SIQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\iti\Clothing-Web-Portal\Process_Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ganna\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A26CE9B-A485-45DF-B056-FD631943FDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD300822-133F-475C-A4B4-5599E80EB993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SIQ" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="325">
   <si>
     <t>SIQ ID</t>
   </si>
@@ -1360,12 +1358,63 @@
   <si>
     <t>E-mail will be sent on first request and E-mail will be sent on delivery.</t>
   </si>
+  <si>
+    <t>does the system have the ability to update quantities and remove items from the cart?</t>
+  </si>
+  <si>
+    <t>in the cart page the system should display the total price only or the price for each product and total price?</t>
+  </si>
+  <si>
+    <t>admin can add new products if yes, he will also assign a supplier for them?</t>
+  </si>
+  <si>
+    <t>SIQ_ Generic_02</t>
+  </si>
+  <si>
+    <t>SIQ_Reg_07</t>
+  </si>
+  <si>
+    <t>SIQ_Cart_02</t>
+  </si>
+  <si>
+    <t>SIQ_Cart_03</t>
+  </si>
+  <si>
+    <t>SIQ_Admin_04</t>
+  </si>
+  <si>
+    <t>What are the supported browsers and versions?</t>
+  </si>
+  <si>
+    <t>what are the verification methods in the registration page?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">example if an input field is less or more than its range what the system should display (the error message) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes all browser </t>
+  </si>
+  <si>
+    <t>error message relevant to it</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>both</t>
+  </si>
+  <si>
+    <t>Do you want the navigation bar to have a drop-down menu with the login and sign-up options, or should the two buttons be side by side?</t>
+  </si>
+  <si>
+    <t>two buttons side by side</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1436,6 +1485,11 @@
       <color theme="1"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1499,7 +1553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1608,6 +1662,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2144,22 +2201,91 @@
       </c>
     </row>
     <row r="19" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E20" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B19" t="s">
+        <v>316</v>
+      </c>
+      <c r="D19" t="s">
+        <v>319</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="D20" t="s">
+        <v>320</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D21" t="s">
+        <v>321</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="22" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D22" t="s">
+        <v>322</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="23" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E23" s="3"/>
+      <c r="A23" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D23" t="s">
+        <v>321</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="24" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B24" t="s">
+        <v>323</v>
+      </c>
+      <c r="D24" t="s">
+        <v>324</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="25" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E25" s="3"/>
@@ -5085,8 +5211,9 @@
       <c r="E959" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E14:E959 E1:E13" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E1:E959" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"In Disscusion ,Approved ,N/A,Status"</formula1>
     </dataValidation>
   </dataValidations>
